--- a/data/trans_camb/P11_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P11_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 2,07</t>
+          <t>-3,98; 2,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 0,9</t>
+          <t>-5,33; 1,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 6,16</t>
+          <t>-4,02; 6,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 5,91</t>
+          <t>-1,34; 5,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 2,45</t>
+          <t>-4,39; 2,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 9,96</t>
+          <t>-1,02; 10,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 2,86</t>
+          <t>-1,63; 3,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 0,71</t>
+          <t>-3,96; 0,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 6,27</t>
+          <t>-1,69; 5,57</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-49,65; 46,37</t>
+          <t>-48,84; 46,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-64,89; 23,05</t>
+          <t>-63,86; 24,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-51,01; 113,49</t>
+          <t>-53,31; 120,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-23,38; 99,77</t>
+          <t>-17,32; 106,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,81; 47,82</t>
+          <t>-50,37; 52,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,07; 164,48</t>
+          <t>-12,3; 181,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,19; 51,38</t>
+          <t>-20,69; 55,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-48,47; 13,98</t>
+          <t>-49,98; 9,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-17,22; 107,27</t>
+          <t>-23,09; 90,96</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 5,37</t>
+          <t>-0,28; 5,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 5,56</t>
+          <t>-0,53; 5,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,98; 14,38</t>
+          <t>5,53; 15,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,75; -1,5</t>
+          <t>-8,84; -1,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 0,41</t>
+          <t>-7,33; 0,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 4,64</t>
+          <t>-6,2; 4,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 1,47</t>
+          <t>-3,19; 1,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 2,44</t>
+          <t>-2,44; 2,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 8,39</t>
+          <t>1,14; 8,5</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 113,7</t>
+          <t>-4,91; 113,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 123,66</t>
+          <t>-9,76; 116,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>74,14; 306,55</t>
+          <t>80,21; 334,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-54,66; -10,84</t>
+          <t>-55,54; -9,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,4; 3,72</t>
+          <t>-45,76; 4,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-39,05; 35,05</t>
+          <t>-39,48; 37,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,35; 17,05</t>
+          <t>-29,68; 16,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-22,67; 28,75</t>
+          <t>-23,09; 27,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,26; 97,29</t>
+          <t>10,8; 98,0</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 5,41</t>
+          <t>-1,78; 5,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 4,68</t>
+          <t>-2,87; 4,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,21; 12,52</t>
+          <t>4,39; 12,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 3,01</t>
+          <t>-5,63; 2,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,01; -1,57</t>
+          <t>-9,83; -1,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 7,0</t>
+          <t>-1,73; 6,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 2,84</t>
+          <t>-2,83; 2,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 0,21</t>
+          <t>-5,48; 0,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,99; 8,1</t>
+          <t>2,28; 7,94</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-15,42; 60,67</t>
+          <t>-14,67; 61,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-21,69; 53,88</t>
+          <t>-23,77; 49,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33,25; 140,12</t>
+          <t>35,38; 134,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-25,14; 16,06</t>
+          <t>-25,44; 14,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-45,3; -8,51</t>
+          <t>-42,51; -8,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 39,13</t>
+          <t>-7,59; 35,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-16,5; 20,1</t>
+          <t>-16,23; 20,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-30,97; 1,37</t>
+          <t>-31,6; 0,14</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,1; 55,04</t>
+          <t>13,25; 56,28</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 0,08</t>
+          <t>-8,87; 0,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 5,15</t>
+          <t>-4,28; 5,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,98; 9,83</t>
+          <t>-11,66; 10,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 2,62</t>
+          <t>-8,57; 2,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,53; -0,94</t>
+          <t>-11,43; -0,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 9,02</t>
+          <t>-2,34; 9,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 0,23</t>
+          <t>-7,17; 0,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 0,75</t>
+          <t>-6,38; 0,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 7,88</t>
+          <t>-8,65; 7,83</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-42,22; 0,53</t>
+          <t>-41,15; 3,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-21,6; 32,75</t>
+          <t>-20,63; 33,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-55,87; 56,4</t>
+          <t>-54,89; 57,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-26,47; 9,28</t>
+          <t>-26,09; 10,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-35,72; -3,32</t>
+          <t>-34,48; -2,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 33,34</t>
+          <t>-7,1; 34,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-27,3; 0,92</t>
+          <t>-27,74; 0,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-23,88; 3,58</t>
+          <t>-24,34; 3,78</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-36,17; 33,49</t>
+          <t>-33,92; 33,45</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 1,99</t>
+          <t>-10,95; 2,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-12,28; -0,29</t>
+          <t>-11,98; 0,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,28; 14,8</t>
+          <t>2,41; 14,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,17; 15,11</t>
+          <t>0,41; 14,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 10,08</t>
+          <t>-3,73; 9,96</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,56; 12,89</t>
+          <t>1,38; 13,19</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 6,57</t>
+          <t>-2,73; 6,59</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 3,14</t>
+          <t>-6,29; 2,76</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,51; 11,72</t>
+          <t>3,59; 11,97</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-30,92; 7,2</t>
+          <t>-31,16; 9,34</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-35,91; -0,66</t>
+          <t>-35,52; 0,29</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6,69; 56,22</t>
+          <t>7,1; 54,91</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2,61; 43,18</t>
+          <t>0,99; 41,24</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 28,76</t>
+          <t>-8,97; 28,28</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,59; 37,53</t>
+          <t>3,4; 38,44</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 20,33</t>
+          <t>-7,39; 19,88</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-16,1; 9,89</t>
+          <t>-16,65; 8,37</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>9,47; 36,34</t>
+          <t>9,6; 36,53</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 10,87</t>
+          <t>-4,86; 11,28</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 1,94</t>
+          <t>-13,19; 2,28</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 4,96</t>
+          <t>-8,55; 4,47</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 12,41</t>
+          <t>-2,12; 11,7</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 6,71</t>
+          <t>-7,78; 6,37</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 36,2</t>
+          <t>-4,64; 34,64</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 9,5</t>
+          <t>-1,75; 9,14</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 1,96</t>
+          <t>-8,49; 2,03</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 33,55</t>
+          <t>-4,17; 31,86</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-14,35; 31,74</t>
+          <t>-11,94; 33,86</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-31,1; 6,09</t>
+          <t>-32,13; 7,1</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-20,49; 14,72</t>
+          <t>-20,11; 14,14</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 24,7</t>
+          <t>-3,5; 22,77</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 13,77</t>
+          <t>-13,5; 12,16</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 72,25</t>
+          <t>-8,56; 69,19</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 21,29</t>
+          <t>-3,54; 20,79</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-17,6; 4,58</t>
+          <t>-17,16; 4,45</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 75,14</t>
+          <t>-8,75; 70,76</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 9,94</t>
+          <t>-9,58; 8,61</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-16,0; 2,17</t>
+          <t>-14,9; 1,18</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-17,7; -1,52</t>
+          <t>-16,84; -1,16</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,8; 17,0</t>
+          <t>3,32; 16,58</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 9,16</t>
+          <t>-6,72; 8,8</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,11; 16,2</t>
+          <t>4,54; 16,67</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 10,93</t>
+          <t>0,67; 11,07</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 3,79</t>
+          <t>-7,28; 4,24</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 7,52</t>
+          <t>-2,36; 7,49</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-13,56; 17,63</t>
+          <t>-14,66; 15,34</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-24,36; 3,41</t>
+          <t>-23,14; 2,04</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-27,28; -3,14</t>
+          <t>-25,93; -2,47</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4,03; 27,2</t>
+          <t>4,8; 26,43</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 14,09</t>
+          <t>-9,25; 14,09</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,66; 25,53</t>
+          <t>6,17; 26,83</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 17,51</t>
+          <t>1,08; 18,12</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 6,28</t>
+          <t>-10,76; 6,88</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 11,99</t>
+          <t>-3,44; 12,13</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 2,72</t>
+          <t>-1,11; 2,62</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 2,4</t>
+          <t>-1,34; 2,31</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1,07; 9,42</t>
+          <t>0,97; 9,5</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 4,38</t>
+          <t>-0,06; 4,39</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 1,66</t>
+          <t>-2,61; 1,93</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>6,26; 22,25</t>
+          <t>6,38; 22,0</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 2,91</t>
+          <t>0,03; 2,94</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 1,49</t>
+          <t>-1,37; 1,51</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>5,51; 15,81</t>
+          <t>5,71; 15,21</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 15,82</t>
+          <t>-5,86; 14,92</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 14,26</t>
+          <t>-7,04; 13,51</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6,22; 53,24</t>
+          <t>6,48; 55,0</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 15,5</t>
+          <t>-0,1; 15,6</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 5,84</t>
+          <t>-8,68; 6,91</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>21,23; 78,83</t>
+          <t>21,61; 76,75</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 12,62</t>
+          <t>0,27; 12,91</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 6,54</t>
+          <t>-5,58; 6,51</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>22,45; 65,63</t>
+          <t>23,19; 66,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P11_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P11_R-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>1,68</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,03</t>
+          <t>4,91</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,81</t>
+          <t>3,19</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 2,23</t>
+          <t>-3,86; 2,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 1,09</t>
+          <t>-5,44; 0,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 6,49</t>
+          <t>-2,7; 6,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 5,79</t>
+          <t>-1,7; 5,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 2,82</t>
+          <t>-4,08; 2,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 10,2</t>
+          <t>0,52; 10,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 3,03</t>
+          <t>-1,95; 2,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 0,47</t>
+          <t>-3,79; 0,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 5,57</t>
+          <t>-0,08; 7,0</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>46,99%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-48,84; 46,67</t>
+          <t>-48,22; 47,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-63,86; 24,48</t>
+          <t>-68,23; 16,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-53,31; 120,34</t>
+          <t>-37,6; 132,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,32; 106,14</t>
+          <t>-21,18; 100,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-50,37; 52,77</t>
+          <t>-47,64; 48,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,3; 181,37</t>
+          <t>2,71; 188,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,69; 55,02</t>
+          <t>-24,86; 45,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-49,98; 9,65</t>
+          <t>-48,81; 16,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-23,09; 90,96</t>
+          <t>-2,51; 119,18</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9,51</t>
+          <t>9,8</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>1,31</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,07</t>
+          <t>5,89</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 5,25</t>
+          <t>-0,13; 5,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 5,42</t>
+          <t>-0,19; 5,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,53; 15,28</t>
+          <t>5,04; 14,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,84; -1,24</t>
+          <t>-8,89; -1,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 0,43</t>
+          <t>-7,15; 0,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 4,94</t>
+          <t>-3,09; 5,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 1,35</t>
+          <t>-3,25; 1,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 2,26</t>
+          <t>-2,49; 2,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 8,5</t>
+          <t>2,72; 8,99</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>163,61%</t>
+          <t>168,53%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>61,11%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 113,18</t>
+          <t>-3,25; 118,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 116,33</t>
+          <t>-6,16; 121,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80,21; 334,03</t>
+          <t>61,71; 290,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-55,54; -9,69</t>
+          <t>-54,07; -8,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-45,76; 4,34</t>
+          <t>-44,11; 6,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-39,48; 37,33</t>
+          <t>-18,99; 46,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,68; 16,35</t>
+          <t>-30,18; 14,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,09; 27,24</t>
+          <t>-23,79; 24,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,8; 98,0</t>
+          <t>24,39; 103,81</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8,12</t>
+          <t>7,69</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,54</t>
+          <t>2,35</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,15</t>
+          <t>4,84</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 5,25</t>
+          <t>-1,79; 5,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 4,27</t>
+          <t>-3,05; 4,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,39; 12,53</t>
+          <t>3,92; 11,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 2,58</t>
+          <t>-6,0; 2,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,83; -1,6</t>
+          <t>-10,08; -2,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 6,45</t>
+          <t>-1,85; 6,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 2,84</t>
+          <t>-2,89; 2,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 0,01</t>
+          <t>-5,68; -0,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,28; 7,94</t>
+          <t>1,95; 7,72</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>30,7%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,67; 61,83</t>
+          <t>-14,87; 61,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,77; 49,25</t>
+          <t>-24,32; 49,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35,38; 134,42</t>
+          <t>29,09; 134,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-25,44; 14,29</t>
+          <t>-26,22; 12,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-42,51; -8,4</t>
+          <t>-44,67; -11,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 35,8</t>
+          <t>-8,63; 37,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-16,23; 20,09</t>
+          <t>-16,72; 19,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-31,6; 0,14</t>
+          <t>-32,97; -0,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,25; 56,28</t>
+          <t>11,09; 54,62</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>7,85</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,95</t>
+          <t>4,57</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,68</t>
+          <t>6,34</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 0,48</t>
+          <t>-9,26; 0,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 5,17</t>
+          <t>-4,25; 5,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 10,0</t>
+          <t>2,45; 12,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 2,89</t>
+          <t>-7,85; 2,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,43; -0,63</t>
+          <t>-11,34; -0,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 9,14</t>
+          <t>-0,26; 9,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 0,03</t>
+          <t>-7,48; -0,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 0,89</t>
+          <t>-6,43; 0,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 7,83</t>
+          <t>2,34; 9,47</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-41,15; 3,46</t>
+          <t>-42,89; 1,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-20,63; 33,0</t>
+          <t>-19,94; 34,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-54,89; 57,66</t>
+          <t>10,98; 78,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-26,09; 10,91</t>
+          <t>-24,76; 9,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-34,48; -2,49</t>
+          <t>-34,77; -3,08</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 34,15</t>
+          <t>-0,68; 35,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-27,74; 0,17</t>
+          <t>-28,39; -1,22</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-24,34; 3,78</t>
+          <t>-24,86; 2,42</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-33,92; 33,45</t>
+          <t>9,19; 43,02</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8,51</t>
+          <t>6,88</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,53</t>
+          <t>7,45</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>7,9</t>
+          <t>7,09</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 2,33</t>
+          <t>-9,89; 2,4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-11,98; 0,04</t>
+          <t>-12,56; 0,01</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,41; 14,66</t>
+          <t>0,95; 12,43</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,41; 14,28</t>
+          <t>1,31; 14,11</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 9,96</t>
+          <t>-3,77; 9,62</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,38; 13,19</t>
+          <t>1,42; 12,97</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 6,59</t>
+          <t>-2,32; 6,61</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 2,76</t>
+          <t>-5,74; 2,92</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,59; 11,97</t>
+          <t>2,97; 11,46</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-31,16; 9,34</t>
+          <t>-29,69; 8,15</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-35,52; 0,29</t>
+          <t>-36,38; 0,74</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7,1; 54,91</t>
+          <t>2,74; 45,4</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0,99; 41,24</t>
+          <t>2,82; 39,96</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 28,28</t>
+          <t>-9,11; 27,75</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,4; 38,44</t>
+          <t>3,35; 38,43</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 19,88</t>
+          <t>-6,19; 21,0</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-16,65; 8,37</t>
+          <t>-15,65; 9,05</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>9,6; 36,53</t>
+          <t>8,0; 36,53</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-2,05</t>
+          <t>-2,83</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,42</t>
+          <t>-2,39</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8,97</t>
+          <t>-2,96</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 11,28</t>
+          <t>-6,0; 9,83</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 2,28</t>
+          <t>-13,39; 1,82</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 4,47</t>
+          <t>-9,4; 4,03</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 11,7</t>
+          <t>-2,61; 12,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 6,37</t>
+          <t>-7,78; 7,17</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 34,64</t>
+          <t>-8,32; 3,36</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 9,14</t>
+          <t>-1,96; 9,2</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 2,03</t>
+          <t>-8,56; 2,37</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 31,86</t>
+          <t>-7,3; 1,9</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-5,43%</t>
+          <t>-7,49%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>-4,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>-6,33%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 33,86</t>
+          <t>-14,06; 28,93</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-32,13; 7,1</t>
+          <t>-31,15; 5,84</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-20,11; 14,14</t>
+          <t>-22,19; 12,92</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 22,77</t>
+          <t>-4,43; 22,99</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 12,16</t>
+          <t>-13,44; 14,26</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 69,19</t>
+          <t>-14,42; 6,26</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 20,79</t>
+          <t>-3,97; 21,03</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-17,16; 4,45</t>
+          <t>-17,53; 5,51</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 70,76</t>
+          <t>-14,82; 4,44</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-9,46</t>
+          <t>-10,07</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,51</t>
+          <t>9,99</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2,42</t>
+          <t>1,83</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 8,61</t>
+          <t>-9,03; 9,43</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-14,9; 1,18</t>
+          <t>-15,64; 1,43</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-16,84; -1,16</t>
+          <t>-17,77; -2,43</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,32; 16,58</t>
+          <t>2,94; 17,39</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 8,8</t>
+          <t>-7,76; 7,91</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,54; 16,67</t>
+          <t>3,69; 16,12</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,67; 11,07</t>
+          <t>0,48; 11,5</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 4,24</t>
+          <t>-7,78; 3,62</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 7,49</t>
+          <t>-2,76; 6,8</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-15,54%</t>
+          <t>-16,54%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 15,34</t>
+          <t>-14,2; 17,09</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-23,14; 2,04</t>
+          <t>-24,08; 2,48</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-25,93; -2,47</t>
+          <t>-26,72; -4,31</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4,8; 26,43</t>
+          <t>4,12; 27,21</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 14,09</t>
+          <t>-10,73; 12,26</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,17; 26,83</t>
+          <t>4,96; 25,45</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,08; 18,12</t>
+          <t>0,69; 18,7</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 6,88</t>
+          <t>-11,38; 5,79</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 12,13</t>
+          <t>-4,05; 10,84</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6,69</t>
+          <t>8,27</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,0</t>
+          <t>7,93</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>8,98</t>
+          <t>8,16</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 2,62</t>
+          <t>-1,23; 2,61</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 2,31</t>
+          <t>-1,61; 2,23</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,97; 9,5</t>
+          <t>6,12; 10,19</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 4,39</t>
+          <t>-0,24; 4,36</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 1,93</t>
+          <t>-2,73; 1,7</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>6,38; 22,0</t>
+          <t>5,7; 9,94</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,03; 2,94</t>
+          <t>-0,13; 2,85</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,51</t>
+          <t>-1,48; 1,55</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>5,71; 15,21</t>
+          <t>6,68; 9,73</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>34,32%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 14,92</t>
+          <t>-6,4; 15,18</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 13,51</t>
+          <t>-8,49; 12,95</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6,48; 55,0</t>
+          <t>31,52; 58,28</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 15,6</t>
+          <t>-0,81; 15,43</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 6,91</t>
+          <t>-9,02; 6,03</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>21,61; 76,75</t>
+          <t>18,85; 35,22</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>0,27; 12,91</t>
+          <t>-0,57; 12,3</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 6,51</t>
+          <t>-5,99; 6,77</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>23,19; 66,02</t>
+          <t>27,2; 42,52</t>
         </is>
       </c>
     </row>
